--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486326_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486326_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.1361</v>
+        <v>7.8982</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3764</v>
+        <v>4.8919</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7597</v>
+        <v>3.0063</v>
       </c>
       <c r="G2" t="n">
         <v>9.5411</v>
@@ -610,13 +610,13 @@
         <v>1.305</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2947</v>
+        <v>0.4675</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.2379</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4588</v>
+        <v>0.7054</v>
       </c>
       <c r="V2" t="n">
         <v>0.9347</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. BRIMAH</t>
+          <t>T. MC GREW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5982</v>
+        <v>3.3125</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9954</v>
+        <v>1.2073</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6028</v>
+        <v>2.1052</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.1879</v>
+        <v>1.6125</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.2055</v>
+        <v>2.579</v>
       </c>
       <c r="I3" t="n">
-        <v>2.0176</v>
+        <v>-0.9666</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.8762</v>
+        <v>2.4182</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.8707</v>
+        <v>2.6644</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9945000000000001</v>
+        <v>-0.2462</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6883</v>
+        <v>-0.8057</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3348</v>
+        <v>-0.0854</v>
       </c>
       <c r="O3" t="n">
-        <v>1.0231</v>
+        <v>-0.7204</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.2175</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R3" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5262</v>
+        <v>1.1128</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6992</v>
+        <v>0.2464</v>
       </c>
       <c r="U3" t="n">
-        <v>0.827</v>
+        <v>0.8663999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>2.2599</v>
+        <v>0.3698</v>
       </c>
       <c r="W3" t="n">
-        <v>2.2599</v>
+        <v>-0.3698</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. NWOGBO</t>
+          <t>S. SALIN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2985</v>
+        <v>2.9637</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2527</v>
+        <v>1.9246</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0457</v>
+        <v>1.0392</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.3027</v>
+        <v>0.6322</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9306</v>
+        <v>-0.7241</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3721</v>
+        <v>1.3563</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7781</v>
+        <v>1.5058</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6633</v>
+        <v>0.2587</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1147</v>
+        <v>1.2471</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0808</v>
+        <v>-0.8736</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.5939</v>
+        <v>-0.9827</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4869</v>
+        <v>0.1091</v>
       </c>
       <c r="P4" t="n">
-        <v>1.0875</v>
+        <v>0.2175</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6648</v>
+        <v>0.4191</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3447</v>
+        <v>-0.1887</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3201</v>
+        <v>0.6077</v>
       </c>
       <c r="V4" t="n">
-        <v>1.8488</v>
+        <v>1.695</v>
       </c>
       <c r="W4" t="n">
-        <v>1.13</v>
+        <v>1.695</v>
       </c>
       <c r="X4" t="n">
-        <v>0.7188</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. SALIN</t>
+          <t>A. BRIMAH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8529</v>
+        <v>2.6541</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9678</v>
+        <v>-0.0104</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8851</v>
+        <v>2.6645</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6322</v>
+        <v>-1.1879</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7241</v>
+        <v>-3.2055</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3563</v>
+        <v>2.0176</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5058</v>
+        <v>-1.8762</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2587</v>
+        <v>-2.8707</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2471</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8736</v>
+        <v>0.6883</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9827</v>
+        <v>-0.3348</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1091</v>
+        <v>1.0231</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2175</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3082</v>
+        <v>1.582</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1454</v>
+        <v>0.6934</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4536</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>1.695</v>
+        <v>2.2599</v>
       </c>
       <c r="W5" t="n">
-        <v>1.695</v>
+        <v>2.2599</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. VAULET</t>
+          <t>L. NWOGBO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.7942</v>
+        <v>2.5529</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1118</v>
+        <v>2.3839</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6824</v>
+        <v>0.169</v>
       </c>
       <c r="G6" t="n">
-        <v>3.0592</v>
+        <v>-1.3027</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5388</v>
+        <v>-0.9306</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5204</v>
+        <v>-0.3721</v>
       </c>
       <c r="J6" t="n">
-        <v>3.0363</v>
+        <v>0.7781</v>
       </c>
       <c r="K6" t="n">
-        <v>2.1566</v>
+        <v>0.6633</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8797</v>
+        <v>0.1147</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0229</v>
+        <v>-2.0808</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6178</v>
+        <v>-1.5939</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6407</v>
+        <v>-0.4869</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S6" t="n">
-        <v>2.5191</v>
+        <v>0.9193</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5997</v>
+        <v>0.4759</v>
       </c>
       <c r="U6" t="n">
-        <v>1.9194</v>
+        <v>0.4434</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.479</v>
+        <v>1.8488</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3491</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.13</v>
+        <v>0.7188</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. MC GREW</t>
+          <t>J. VAULET</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.1466</v>
+        <v>1.4032</v>
       </c>
       <c r="E7" t="n">
-        <v>0.288</v>
+        <v>0.553</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8586</v>
+        <v>0.8502</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6125</v>
+        <v>3.0592</v>
       </c>
       <c r="H7" t="n">
-        <v>2.579</v>
+        <v>1.5388</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9666</v>
+        <v>1.5204</v>
       </c>
       <c r="J7" t="n">
-        <v>2.4182</v>
+        <v>3.0363</v>
       </c>
       <c r="K7" t="n">
-        <v>2.6644</v>
+        <v>2.1566</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.2462</v>
+        <v>0.8797</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8057</v>
+        <v>0.0229</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0854</v>
+        <v>-0.6178</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7204</v>
+        <v>0.6407</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2175</v>
+        <v>-1.305</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R7" t="n">
-        <v>1.305</v>
+        <v>0.87</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0531</v>
+        <v>1.1281</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6729000000000001</v>
+        <v>0.0409</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6198</v>
+        <v>1.0872</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3698</v>
+        <v>-1.479</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3698</v>
+        <v>-0.3491</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7395</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6382</v>
+        <v>1.1345</v>
       </c>
       <c r="E8" t="n">
-        <v>1.8221</v>
+        <v>2.2259</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1838</v>
+        <v>-1.0914</v>
       </c>
       <c r="G8" t="n">
         <v>-0.244</v>
@@ -1078,13 +1078,13 @@
         <v>0.87</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5772</v>
+        <v>1.0734</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0649</v>
+        <v>0.3389</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6421</v>
+        <v>0.7345</v>
       </c>
       <c r="V8" t="n">
         <v>-0.5649999999999999</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. LOPEZ BARRANTES</t>
+          <t>O. SILVERIO GRULLON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.604</v>
+        <v>1.1052</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0805</v>
+        <v>0.0717</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6845</v>
+        <v>1.0334</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5681</v>
+        <v>1.1514</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7633</v>
+        <v>-0.2495</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1952</v>
+        <v>1.4009</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0565</v>
+        <v>1.9572</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0182</v>
+        <v>-0.0151</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0382</v>
+        <v>1.9723</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5116000000000001</v>
+        <v>-0.8057</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7451</v>
+        <v>-0.2344</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2335</v>
+        <v>-0.5714</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0359</v>
+        <v>1.2588</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.137</v>
+        <v>0.2896</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1729</v>
+        <v>0.9692</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. GARINO GULLOTTA</t>
+          <t>H. LOPEZ BARRANTES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0973</v>
+        <v>0.5732</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5373</v>
+        <v>-0.0805</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6346</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>1.8991</v>
+        <v>0.5681</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.8223</v>
+        <v>0.7633</v>
       </c>
       <c r="I10" t="n">
-        <v>4.7214</v>
+        <v>-0.1952</v>
       </c>
       <c r="J10" t="n">
-        <v>1.8587</v>
+        <v>0.0565</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.3925</v>
+        <v>0.0182</v>
       </c>
       <c r="L10" t="n">
-        <v>3.2512</v>
+        <v>0.0382</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0404</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.4298</v>
+        <v>0.7451</v>
       </c>
       <c r="O10" t="n">
-        <v>1.4702</v>
+        <v>-0.2335</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0875</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5685</v>
+        <v>0.0051</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1334</v>
+        <v>-0.137</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7019</v>
+        <v>0.1421</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>O. SILVERIO GRULLON</t>
+          <t>P. GARINO GULLOTTA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.081</v>
+        <v>0.5319</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8908</v>
+        <v>-1.1335</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9718</v>
+        <v>1.6654</v>
       </c>
       <c r="G11" t="n">
-        <v>1.1514</v>
+        <v>1.8991</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2495</v>
+        <v>-2.8223</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4009</v>
+        <v>4.7214</v>
       </c>
       <c r="J11" t="n">
-        <v>1.9572</v>
+        <v>1.8587</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.0151</v>
+        <v>-1.3925</v>
       </c>
       <c r="L11" t="n">
-        <v>1.9723</v>
+        <v>3.2512</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8057</v>
+        <v>0.0404</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2344</v>
+        <v>-1.4298</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5714</v>
+        <v>1.4702</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.305</v>
+        <v>-2.1751</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.1751</v>
+        <v>-3.2626</v>
       </c>
       <c r="R11" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2346</v>
+        <v>1.0031</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6729000000000001</v>
+        <v>0.2704</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9075</v>
+        <v>0.7327</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0081</v>
+        <v>-0.2055</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.0591</v>
+        <v>-1.1024</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0509</v>
+        <v>0.8968</v>
       </c>
       <c r="G12" t="n">
         <v>-1.1864</v>
@@ -1390,13 +1390,13 @@
         <v>1.0875</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1783</v>
+        <v>0.9809</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0601</v>
+        <v>0.0168</v>
       </c>
       <c r="U12" t="n">
-        <v>1.1182</v>
+        <v>0.9641</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>23.2389</v>
+        <v>23.9239</v>
       </c>
       <c r="E13" t="n">
-        <v>10.2465</v>
+        <v>10.9315</v>
       </c>
       <c r="F13" t="n">
         <v>12.9923</v>
@@ -1435,7 +1435,7 @@
         <v>14.5426</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4101000000000001</v>
+        <v>0.4101000000000008</v>
       </c>
       <c r="I13" t="n">
         <v>14.1324</v>
@@ -1444,7 +1444,7 @@
         <v>20.1146</v>
       </c>
       <c r="K13" t="n">
-        <v>5.583399999999999</v>
+        <v>5.583400000000001</v>
       </c>
       <c r="L13" t="n">
         <v>14.5309</v>
@@ -1468,10 +1468,10 @@
         <v>10.875</v>
       </c>
       <c r="S13" t="n">
-        <v>9.265000000000001</v>
+        <v>9.950100000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1237</v>
+        <v>1.8087</v>
       </c>
       <c r="U13" t="n">
         <v>8.141300000000001</v>
@@ -1480,16 +1480,16 @@
         <v>4.869000000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>5.3214</v>
+        <v>5.321400000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.4525999999999999</v>
+        <v>-0.4525999999999997</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. MARTIN</t>
+          <t>P. RODRIGUEZ PASCUAL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5203</v>
+        <v>1.232</v>
       </c>
       <c r="E14" t="n">
-        <v>2.193</v>
+        <v>1.0418</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6728</v>
+        <v>0.1903</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.5639999999999999</v>
+        <v>1.086</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5595</v>
+        <v>-0.1642</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.1236</v>
+        <v>1.2503</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4737</v>
+        <v>1.204</v>
       </c>
       <c r="K14" t="n">
-        <v>1.4084</v>
+        <v>0.0182</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.9347</v>
+        <v>1.1857</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.0377</v>
+        <v>-0.118</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8488</v>
+        <v>-0.1825</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1889</v>
+        <v>0.0645</v>
       </c>
       <c r="P14" t="n">
-        <v>1.305</v>
+        <v>0.2175</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.305</v>
+        <v>0.2175</v>
       </c>
       <c r="S14" t="n">
-        <v>0.584</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3942</v>
+        <v>-0.1622</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1899</v>
+        <v>0.0907</v>
       </c>
       <c r="V14" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. RODRIGUEZ PASCUAL</t>
+          <t>C. MARTIN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1819</v>
+        <v>0.4297</v>
       </c>
       <c r="E15" t="n">
-        <v>0.93</v>
+        <v>1.4107</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2519</v>
+        <v>-0.981</v>
       </c>
       <c r="G15" t="n">
-        <v>1.086</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1642</v>
+        <v>0.5595</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2503</v>
+        <v>-1.1236</v>
       </c>
       <c r="J15" t="n">
-        <v>1.204</v>
+        <v>0.4737</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0182</v>
+        <v>1.4084</v>
       </c>
       <c r="L15" t="n">
-        <v>1.1857</v>
+        <v>-0.9347</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.118</v>
+        <v>-1.0377</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1825</v>
+        <v>-0.8488</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0645</v>
+        <v>-0.1889</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2175</v>
+        <v>1.305</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2175</v>
+        <v>1.305</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1216</v>
+        <v>-0.5065</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.274</v>
+        <v>-0.3881</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1524</v>
+        <v>-0.1184</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.3252</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2258</v>
+        <v>-0.0524</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2175</v>
+        <v>-0.1057</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.0533</v>
       </c>
       <c r="G16" t="n">
         <v>-0.0615</v>
@@ -1702,13 +1702,13 @@
         <v>0.2175</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3819</v>
+        <v>-0.2085</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.274</v>
+        <v>-0.1622</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1079</v>
+        <v>-0.0463</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.701</v>
+        <v>-0.4428</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5103</v>
+        <v>1.3986</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.2113</v>
+        <v>-1.8414</v>
       </c>
       <c r="G17" t="n">
         <v>-0.2644</v>
@@ -1780,13 +1780,13 @@
         <v>1.9576</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9984</v>
+        <v>-0.7402</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4194</v>
+        <v>-0.5311</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.579</v>
+        <v>-0.2091</v>
       </c>
       <c r="V17" t="n">
         <v>-0.3082</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.708</v>
+        <v>-1.577</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3293</v>
+        <v>-1.1058</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3787</v>
+        <v>-0.4712</v>
       </c>
       <c r="G18" t="n">
         <v>-1.0694</v>
@@ -1858,13 +1858,13 @@
         <v>1.0875</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1612</v>
+        <v>-1.0302</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9589</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2023</v>
+        <v>-0.2947</v>
       </c>
       <c r="V18" t="n">
         <v>-0.5649999999999999</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. STOLBETSKIY</t>
+          <t>V. ALVES BENITE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9794</v>
+        <v>-1.6704</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.8403</v>
+        <v>-0.9351</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1391</v>
+        <v>-0.7353</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.0703</v>
+        <v>-0.6505</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.0041</v>
+        <v>0.4746</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.06619999999999999</v>
+        <v>-1.1252</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.8319</v>
+        <v>3.0646</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.8702</v>
+        <v>1.3235</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0382</v>
+        <v>1.7412</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2383</v>
+        <v>-3.7151</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1339</v>
+        <v>-0.8488</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1044</v>
+        <v>-2.8663</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6525</v>
+        <v>0.435</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6525</v>
+        <v>2.6101</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5617</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-1.0851</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5533</v>
+        <v>0.4828</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.8525</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.113</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V. ALVES BENITE</t>
+          <t>L. NIKKARINEN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1624</v>
+        <v>-1.9457</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4939</v>
+        <v>-0.1018</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6685</v>
+        <v>-1.8439</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6505</v>
+        <v>-0.4444</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4746</v>
+        <v>-1.3687</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.1252</v>
+        <v>0.9243</v>
       </c>
       <c r="J20" t="n">
-        <v>3.0646</v>
+        <v>0.6084000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3235</v>
+        <v>-0.6538</v>
       </c>
       <c r="L20" t="n">
-        <v>1.7412</v>
+        <v>1.2622</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.7151</v>
+        <v>-1.0528</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8488</v>
+        <v>-0.7149</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.8663</v>
+        <v>-0.3379</v>
       </c>
       <c r="P20" t="n">
         <v>0.435</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.6101</v>
+        <v>0.435</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0944</v>
+        <v>-1.1762</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.6439</v>
+        <v>-0.7102000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5495</v>
+        <v>-0.466</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.8525</v>
+        <v>-0.7602</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.113</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. NIKKARINEN</t>
+          <t>A. MURPHY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2732</v>
+        <v>-2.0243</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2135</v>
+        <v>-1.9909</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.0597</v>
+        <v>-0.0335</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4444</v>
+        <v>-3.8844</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3687</v>
+        <v>-0.2523</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9243</v>
+        <v>-3.6321</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6084000000000001</v>
+        <v>-1.1797</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6538</v>
+        <v>-0.6475</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2622</v>
+        <v>-0.5323</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0528</v>
+        <v>-2.7047</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7149</v>
+        <v>0.3951</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3379</v>
+        <v>-3.0998</v>
       </c>
       <c r="P21" t="n">
-        <v>0.435</v>
+        <v>1.5225</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.435</v>
+        <v>1.5225</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5037</v>
+        <v>-0.289</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.822</v>
+        <v>-0.8111</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6817</v>
+        <v>0.5221</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.7602</v>
+        <v>0.6264999999999999</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.7602</v>
+        <v>0.6264999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. MURPHY</t>
+          <t>D. STOLBETSKIY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4239</v>
+        <v>-2.2415</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5497</v>
+        <v>-2.2874</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1258</v>
+        <v>0.0459</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.8844</v>
+        <v>-2.0703</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2523</v>
+        <v>-2.0041</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.6321</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.1797</v>
+        <v>-1.8319</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6475</v>
+        <v>-1.8702</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5323</v>
+        <v>0.0382</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.7047</v>
+        <v>-0.2383</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3951</v>
+        <v>-0.1339</v>
       </c>
       <c r="O22" t="n">
-        <v>-3.0998</v>
+        <v>-0.1044</v>
       </c>
       <c r="P22" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6886</v>
+        <v>-0.8238</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.3699</v>
+        <v>-0.4554</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6813</v>
+        <v>-0.3683</v>
       </c>
       <c r="V22" t="n">
-        <v>0.6264999999999999</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.6264999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.2047</v>
+        <v>-3.8745</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2992</v>
+        <v>-2.9639</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9055</v>
+        <v>-0.9106</v>
       </c>
       <c r="G23" t="n">
         <v>-2.1633</v>
@@ -2248,13 +2248,13 @@
         <v>1.305</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.0843</v>
+        <v>-1.7542</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.7809</v>
+        <v>-1.4456</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3034</v>
+        <v>-0.3086</v>
       </c>
       <c r="V23" t="n">
         <v>-0.1745</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.6667</v>
+        <v>-5.1266</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.8552</v>
+        <v>-3.5257</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.8115</v>
+        <v>-1.6009</v>
       </c>
       <c r="G24" t="n">
         <v>-3.6675</v>
@@ -2326,13 +2326,13 @@
         <v>2.1751</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1043</v>
+        <v>-0.5642</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1538</v>
+        <v>-0.8243</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0495</v>
+        <v>0.2602</v>
       </c>
       <c r="V24" t="n">
         <v>-1.9825</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.5959</v>
+        <v>-5.2003</v>
       </c>
       <c r="E25" t="n">
         <v>-3.8272</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.7687</v>
+        <v>-1.3731</v>
       </c>
       <c r="G25" t="n">
         <v>-0.789</v>
@@ -2404,13 +2404,13 @@
         <v>2.8276</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.1491</v>
+        <v>-0.7534999999999999</v>
       </c>
       <c r="T25" t="n">
         <v>-0.8304</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3187</v>
+        <v>0.0769</v>
       </c>
       <c r="V25" t="n">
         <v>-1.0477</v>
@@ -2437,31 +2437,31 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-23.2388</v>
+        <v>-22.4938</v>
       </c>
       <c r="E26" t="n">
-        <v>-12.9925</v>
+        <v>-12.9924</v>
       </c>
       <c r="F26" t="n">
-        <v>-10.2465</v>
+        <v>-9.5014</v>
       </c>
       <c r="G26" t="n">
         <v>-14.5427</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.4102999999999994</v>
+        <v>-0.4103000000000003</v>
       </c>
       <c r="I26" t="n">
         <v>-14.1324</v>
       </c>
       <c r="J26" t="n">
-        <v>5.5719</v>
+        <v>5.571900000000001</v>
       </c>
       <c r="K26" t="n">
         <v>5.1731</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3984999999999999</v>
+        <v>0.3985000000000003</v>
       </c>
       <c r="M26" t="n">
         <v>-20.1145</v>
@@ -2482,13 +2482,13 @@
         <v>16.3129</v>
       </c>
       <c r="S26" t="n">
-        <v>-9.265200000000002</v>
+        <v>-8.520100000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>-8.141400000000001</v>
+        <v>-8.1411</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.1237</v>
+        <v>-0.3787</v>
       </c>
       <c r="V26" t="n">
         <v>-4.8689</v>
